--- a/output/pdf_financials_xlsx/CNQ.xlsx
+++ b/output/pdf_financials_xlsx/CNQ.xlsx
@@ -2341,22 +2341,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>4844</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4880</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>5483</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4858</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5186</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>5161</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -7407,22 +7407,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>4844</v>
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>4880</v>
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>5483</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>4858</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>5186</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>5161</v>
+        <v>0</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
@@ -42597,7 +42597,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E402" s="5" t="n">

--- a/output/pdf_financials_xlsx/CNQ.xlsx
+++ b/output/pdf_financials_xlsx/CNQ.xlsx
@@ -2341,22 +2341,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>4844</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>4880</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>5483</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>4858</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>5186</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>5161</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -7407,22 +7407,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4844</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>4880</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>5483</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>4858</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5186</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5161</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
@@ -42597,7 +42597,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E402" s="5" t="n">

--- a/output/pdf_financials_xlsx/CNQ.xlsx
+++ b/output/pdf_financials_xlsx/CNQ.xlsx
@@ -1392,35 +1392,23 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>3005</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4356</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-898</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-822</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>2965</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1475,13 +1463,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-31</v>
+        <v>-735</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-807</v>
+        <v>-427</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-231</v>
+        <v>261</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>618</v>
@@ -1708,35 +1696,23 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3929</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-637</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-204</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2397</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2591</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1930,35 +1906,23 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3929</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-637</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-204</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2397</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2591</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -2258,35 +2222,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>3005</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4356</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-898</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-822</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2233</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>2965</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2410,35 +2362,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>7849</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>9236</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>4585</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>4036</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>7419</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>8126</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2492,35 +2432,23 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>48.61567048621864</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>48.963579494248</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>37.08646768583677</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>35.31985648026604</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>42.78053281051782</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>38.64555095829172</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2574,35 +2502,23 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>24.45923460898502</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>9.80257116620753</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-29.06458797327394</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-75.18248175182481</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>7.344379758172861</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>12.61382799325464</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -2656,35 +2572,23 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>14.06008052028492</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>20.8291364046016</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-5.152471083070452</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-1.785245471252297</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>13.82193518625303</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>12.32225234222666</v>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
@@ -7324,35 +7228,23 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>2270</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>3929</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-637</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-204</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>2397</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>2591</v>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
@@ -9541,13 +9433,13 @@
         <v>19391</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>17262</v>
+        <v>7444</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>27817</v>
+        <v>-1045</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>21685</v>
+        <v>8527</v>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
@@ -33714,7 +33606,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -36010,7 +35906,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -40776,7 +40676,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>31</v>
       </c>
@@ -43732,7 +43636,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -43993,7 +43901,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -45527,7 +45439,11 @@
           <t>Current income tax recovery 12</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -45705,7 +45621,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -45962,7 +45882,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E417" s="5" t="n">
         <v>2270</v>
       </c>
@@ -46739,7 +46663,11 @@
           <t>Current income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -46826,7 +46754,11 @@
           <t>Deferred income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -46913,7 +46845,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -48046,7 +47982,11 @@
           <t>Current income tax (recovery) expense 11</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E441" s="5" t="n">
         <v>735</v>
       </c>
@@ -48224,7 +48164,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E443" s="5" t="n">
         <v>2270</v>
       </c>
